--- a/Result/profitability/3130.xlsx
+++ b/Result/profitability/3130.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.89</v>
       </c>
       <c r="M2" t="n">
-        <v>3.38625</v>
+        <v>3.57125</v>
       </c>
       <c r="N2" t="n">
-        <v>82.28625000000001</v>
+        <v>82.2325</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.19</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0925</v>
+        <v>3.54625</v>
       </c>
       <c r="N3" t="n">
-        <v>77.96125000000001</v>
+        <v>78.23</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.97</v>
       </c>
       <c r="M4" t="n">
-        <v>3.04</v>
+        <v>3.39375</v>
       </c>
       <c r="N4" t="n">
-        <v>73.605</v>
+        <v>73.8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7675</v>
+        <v>2.9575</v>
       </c>
       <c r="N5" t="n">
-        <v>68.16374999999999</v>
+        <v>68.33625000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.67</v>
       </c>
       <c r="M6" t="n">
-        <v>2.28875</v>
+        <v>2.50875</v>
       </c>
       <c r="N6" t="n">
-        <v>62.75375</v>
+        <v>62.9275</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.72</v>
       </c>
       <c r="M7" t="n">
-        <v>1.97125</v>
+        <v>2.38</v>
       </c>
       <c r="N7" t="n">
-        <v>57.31874999999999</v>
+        <v>57.6775</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1.74</v>
       </c>
       <c r="M8" t="n">
-        <v>1.845</v>
+        <v>2.15125</v>
       </c>
       <c r="N8" t="n">
-        <v>51.995</v>
+        <v>52.17625</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>1.4775</v>
       </c>
       <c r="N11" t="n">
-        <v>43.07875</v>
+        <v>43.07875000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>1.5</v>
       </c>
       <c r="N12" t="n">
-        <v>42.47625000000001</v>
+        <v>42.47625</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>1.6</v>
       </c>
       <c r="N13" t="n">
-        <v>42.33374999999999</v>
+        <v>42.33375</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>765</v>
+      </c>
+      <c r="D75" t="n">
+        <v>93</v>
+      </c>
+      <c r="E75" t="n">
+        <v>673</v>
+      </c>
+      <c r="F75" t="n">
+        <v>87.91</v>
+      </c>
+      <c r="G75" t="n">
+        <v>202</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>26.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>37</v>
+      </c>
+      <c r="J75" t="n">
+        <v>240</v>
+      </c>
+      <c r="K75" t="n">
+        <v>200</v>
+      </c>
+      <c r="L75" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.9025</v>
+      </c>
+      <c r="N75" t="n">
+        <v>86.61375000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6862745098039216</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.450000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01677076104557029</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3377777777777777</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.379999999999995</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01594822604876911</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
